--- a/Plantillas para importar.xlsx
+++ b/Plantillas para importar.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promoción 52" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promoción 53" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promoción 58" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promoción 60" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promoción 59" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promoción 60" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +477,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cada hoja de este archivo es un equipo. El nombre de la hoja es el nombre del equipo.</t>
+          <t>Cada hoja es un equipo. El nombre de la hoja es el nombre del equipo.</t>
         </is>
       </c>
     </row>
@@ -666,37 +667,57 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Transcrito de foto: revisar. ¿La lista sigue después del 18?</t>
+          <t>Transcrito de foto: revisar. ¿Sigue después del 18?</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Promoción 59</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Solo 11 jugadores: sin suplentes si juegan 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Promoción 60</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B15" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>170</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
-      <c r="D15" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -997,6 +1018,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Promoción 59</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>11 jugadores · así se llamará el equipo en la app</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Dorsal</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Posicion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Alejandro Moller Faillace</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Alexis Lacan Johnson</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Oscar Alejandro Vissoni Hernandez</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Miguelangel Josue Cruz Sagastume</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Sergio Luis Hernández Linares</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Adam Daniel Cruz Martínez</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>José Enrique Quiñónez Ascencio</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Diego Fernando Rodas Maldonado</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Julio René Estrada Castro</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Justin Enrique Guzmán Muñoz</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Amilcar Daniel Ramírez Ramos</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
